--- a/plano-de-aulas.xlsx
+++ b/plano-de-aulas.xlsx
@@ -216,24 +216,24 @@
     <t xml:space="preserve"> Discussão em sala. Exercícios em sala de aula envolvendo o ambiente OpenAI Gym.  Implementação de agentes autônomos usando o algoritmo Q-Learning.</t>
   </si>
   <si>
+    <t>9-Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiper-parâmetros do algoritmo Q-Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Algoritmo Q-Learning: detalhes e hiperparâmetros. Apresentação do ambiente OpenAI Gym. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercícios em sala de aula envolvendo o ambiente OpenAI Gym.  Implementação de agentes autônomos usando o algoritmo Q-Learning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aula expositiva com resolução de exercícios. Referências: Cap 21 do AIMA, Cap. 18 do Géron e material fornecido pelo professor.</t>
+  </si>
+  <si>
     <t>14-Out</t>
   </si>
   <si>
-    <t xml:space="preserve">Hiper-parâmetros do algoritmo Q-Learning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Algoritmo Q-Learning: detalhes e hiperparâmetros. Apresentação do ambiente OpenAI Gym. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exercícios em sala de aula envolvendo o ambiente OpenAI Gym.  Implementação de agentes autônomos usando o algoritmo Q-Learning.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aula expositiva com resolução de exercícios. Referências: Cap 21 do AIMA, Cap. 18 do Géron e material fornecido pelo professor.</t>
-  </si>
-  <si>
-    <t>19-Out</t>
-  </si>
-  <si>
     <t xml:space="preserve">SARSA: um exemplo de algoritmo on-policy</t>
   </si>
   <si>
@@ -246,7 +246,7 @@
     <t xml:space="preserve"> Aula expositiva com resolução de exercícios. Referências: Cap 21 do AIMA, Cap. 18 do Géron e material fornecido pelo professor.</t>
   </si>
   <si>
-    <t>21-Out</t>
+    <t>16-Out</t>
   </si>
   <si>
     <t xml:space="preserve">Trabalhando com ambientes não-determinísticos</t>
@@ -383,7 +383,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1257,7 +1257,7 @@
       <c r="G18" s="3"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="49.5" customHeight="1">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>66</v>
       </c>
       <c r="B19" s="8"/>
@@ -1276,7 +1276,7 @@
       <c r="G19" s="3"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="49.5" customHeight="1">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>71</v>
       </c>
       <c r="B20" s="3"/>
@@ -1295,7 +1295,7 @@
       <c r="G20" s="3"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>76</v>
       </c>
       <c r="B21" s="1"/>
@@ -1336,7 +1336,7 @@
       <c r="A23" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C23" s="1" t="s">
